--- a/AdditionalData/Tables/pyramid_row Keops_100_IER.xlsx
+++ b/AdditionalData/Tables/pyramid_row Keops_100_IER.xlsx
@@ -49,22 +49,22 @@
     <t xml:space="preserve">distance blocks Horiz (Km)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sum force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Vert. force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Horiz. force blocks (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vert. force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horiz. force blocks row (GJ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total force blocks row (GJ)</t>
+    <t xml:space="preserve">Sum force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Vert. force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sum Horiz. force blocks (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vert. force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horiz. force blocks row (MJ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total force blocks row (MJ)</t>
   </si>
   <si>
     <t xml:space="preserve">% Decrement blocks</t>
